--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484884_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484884_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6867</v>
+        <v>9.2075</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1273</v>
+        <v>5.9656</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5594</v>
+        <v>3.2419</v>
       </c>
       <c r="G2" t="n">
         <v>6.2144</v>
@@ -610,13 +610,13 @@
         <v>2.0757</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4331</v>
+        <v>-0.9123</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.823</v>
+        <v>0.0152</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6101</v>
+        <v>-0.9275</v>
       </c>
       <c r="V2" t="n">
         <v>2.7732</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. CAMARA</t>
+          <t>C. GONZALEZ DIAZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8722</v>
+        <v>4.6288</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4306</v>
+        <v>3.2875</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5584</v>
+        <v>1.3413</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7546</v>
+        <v>1.6445</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7328</v>
+        <v>3.0404</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.9782</v>
+        <v>-1.3959</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8331</v>
+        <v>1.77</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6686</v>
+        <v>2.8635</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1645</v>
+        <v>-1.0935</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0786</v>
+        <v>-0.1255</v>
       </c>
       <c r="N3" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.1769</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.1428</v>
+        <v>-0.3024</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9435</v>
+        <v>1.3209</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R3" t="n">
-        <v>1.887</v>
+        <v>2.2644</v>
       </c>
       <c r="S3" t="n">
-        <v>5.1365</v>
+        <v>-0.1854</v>
       </c>
       <c r="T3" t="n">
-        <v>4.8808</v>
+        <v>0.6122</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2558</v>
+        <v>-0.7976</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9624</v>
+        <v>1.8488</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3398</v>
+        <v>1.8488</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. GONZALEZ DIAZ</t>
+          <t>D. SALVADOR ESCUDER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2604</v>
+        <v>3.5839</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8133</v>
+        <v>0.6483</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4471</v>
+        <v>2.9356</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6445</v>
+        <v>2.1413</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0404</v>
+        <v>0.4805</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3959</v>
+        <v>1.6608</v>
       </c>
       <c r="J4" t="n">
-        <v>1.77</v>
+        <v>0.2804</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8635</v>
+        <v>0.2222</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.0935</v>
+        <v>0.0582</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1255</v>
+        <v>1.8609</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1769</v>
+        <v>0.2583</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3024</v>
+        <v>1.6026</v>
       </c>
       <c r="P4" t="n">
         <v>1.3209</v>
@@ -766,19 +766,19 @@
         <v>2.2644</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4462</v>
+        <v>-1.1235</v>
       </c>
       <c r="T4" t="n">
-        <v>1.138</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6918</v>
+        <v>-1.1897</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8488</v>
+        <v>1.2452</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8488</v>
+        <v>1.2452</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SALVADOR ESCUDER</t>
+          <t>O. CAMARA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5159</v>
+        <v>2.9937</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2874</v>
+        <v>3.605</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8033</v>
+        <v>-0.6113</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1413</v>
+        <v>0.7546</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4805</v>
+        <v>2.7328</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6608</v>
+        <v>-1.9782</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2804</v>
+        <v>2.8331</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2222</v>
+        <v>2.6686</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0582</v>
+        <v>0.1645</v>
       </c>
       <c r="M5" t="n">
-        <v>1.8609</v>
+        <v>-2.0786</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2583</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>1.6026</v>
+        <v>-2.1428</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3209</v>
+        <v>0.9435</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2644</v>
+        <v>1.887</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.1915</v>
+        <v>2.258</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8695000000000001</v>
+        <v>2.0552</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.322</v>
+        <v>0.2029</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2452</v>
+        <v>-0.9624</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2452</v>
+        <v>-0.3398</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. MALONE NAVARRO</t>
+          <t>M. MARISCAL GOMEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2345</v>
+        <v>1.3212</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3788</v>
+        <v>1.5985</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1443</v>
+        <v>-0.2773</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.0923</v>
+        <v>2.0399</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-0.8914</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1321</v>
+        <v>2.9313</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.7619</v>
+        <v>3.4964</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2357</v>
+        <v>-0.9712</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5262</v>
+        <v>4.4676</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3304</v>
+        <v>-1.4565</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2755</v>
+        <v>0.0798</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6059</v>
+        <v>-1.5363</v>
       </c>
       <c r="P6" t="n">
         <v>0.9435</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9435</v>
+        <v>2.8305</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5155</v>
+        <v>-0.1152</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9711</v>
+        <v>0.6307</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4556</v>
+        <v>-0.7459</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8678</v>
+        <v>-1.547</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1696</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3018</v>
+        <v>-0.9054</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. ZOROA GARCIA</t>
+          <t>B. MALONE NAVARRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4443</v>
+        <v>0.9022</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1488</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5931</v>
+        <v>0.1467</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0814</v>
+        <v>-2.0923</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.144</v>
+        <v>-0.9602000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2254</v>
+        <v>-1.1321</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8334</v>
+        <v>-1.7619</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08450000000000001</v>
+        <v>-1.2357</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7489</v>
+        <v>-0.5262</v>
       </c>
       <c r="M7" t="n">
-        <v>0.248</v>
+        <v>-0.3304</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2285</v>
+        <v>0.2755</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4765</v>
+        <v>-0.6059</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1322</v>
+        <v>0.9435</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7548</v>
+        <v>0.9435</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7501</v>
+        <v>0.1833</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3404</v>
+        <v>0.3478</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4097</v>
+        <v>-0.1646</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2452</v>
+        <v>1.8678</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2452</v>
+        <v>2.1696</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MARISCAL GOMEZ</t>
+          <t>E. ZOROA GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1449</v>
+        <v>0.674</v>
       </c>
       <c r="E8" t="n">
-        <v>0.819</v>
+        <v>-0.0514</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6741</v>
+        <v>0.7254</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0399</v>
+        <v>1.0814</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8914</v>
+        <v>-0.144</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9313</v>
+        <v>1.2254</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4964</v>
+        <v>0.8334</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9712</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>4.4676</v>
+        <v>0.7489</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4565</v>
+        <v>0.248</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0798</v>
+        <v>-0.2285</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5363</v>
+        <v>0.4765</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9435</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.887</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8305</v>
+        <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2915</v>
+        <v>-0.5204</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1488</v>
+        <v>-0.243</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1427</v>
+        <v>-0.2774</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.547</v>
+        <v>1.2452</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6415999999999999</v>
+        <v>1.2452</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.393</v>
+        <v>-0.0839</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7644</v>
+        <v>-0.6669</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3714</v>
+        <v>0.583</v>
       </c>
       <c r="G9" t="n">
         <v>-0.169</v>
@@ -1156,13 +1156,13 @@
         <v>0.3774</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6014</v>
+        <v>-0.2923</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2816</v>
+        <v>-0.1842</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3198</v>
+        <v>-0.1081</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4301</v>
+        <v>-2.3049</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5783</v>
+        <v>-1.1886</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8518</v>
+        <v>-1.1163</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0012</v>
@@ -1234,13 +1234,13 @@
         <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0806</v>
+        <v>0.2058</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0864</v>
+        <v>0.4761</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0058</v>
+        <v>-0.2703</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3208</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1796</v>
+        <v>-2.4723</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9091</v>
+        <v>-0.7785</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2705</v>
+        <v>-1.6938</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2371</v>
@@ -1312,13 +1312,13 @@
         <v>1.887</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4915</v>
+        <v>1.1988</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2693</v>
+        <v>0.8613</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7608</v>
+        <v>0.3375</v>
       </c>
       <c r="V11" t="n">
         <v>-1.547</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>18.1562</v>
+        <v>18.4502</v>
       </c>
       <c r="E12" t="n">
-        <v>12.881</v>
+        <v>13.175</v>
       </c>
       <c r="F12" t="n">
         <v>5.2752</v>
@@ -1366,10 +1366,10 @@
         <v>11.8987</v>
       </c>
       <c r="K12" t="n">
-        <v>8.545700000000002</v>
+        <v>8.5457</v>
       </c>
       <c r="L12" t="n">
-        <v>3.353000000000001</v>
+        <v>3.353</v>
       </c>
       <c r="M12" t="n">
         <v>-2.5225</v>
@@ -1390,13 +1390,13 @@
         <v>16.983</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4026999999999998</v>
+        <v>0.6968000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>4.3437</v>
+        <v>4.6375</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.9409</v>
+        <v>-3.940699999999999</v>
       </c>
       <c r="V12" t="n">
         <v>4.603</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.0017</v>
+        <v>2.327</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1012</v>
+        <v>3.614</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0995</v>
+        <v>-1.2871</v>
       </c>
       <c r="G13" t="n">
         <v>1.0391</v>
@@ -1468,13 +1468,13 @@
         <v>1.3209</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0381</v>
+        <v>0.3634</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9246</v>
+        <v>0.4374</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1135</v>
+        <v>-0.074</v>
       </c>
       <c r="V13" t="n">
         <v>0.9244</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. NAVARRO SARMIENTO</t>
+          <t>V. BERENGUER DEL VALLE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4629</v>
+        <v>2.0627</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9727</v>
+        <v>1.2901</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4902</v>
+        <v>0.7726</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4382</v>
+        <v>0.5674</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0188</v>
+        <v>0.1064</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.457</v>
+        <v>0.4609</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0604</v>
+        <v>0.6762</v>
       </c>
       <c r="K14" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0423</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0241</v>
+        <v>0.634</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4986</v>
+        <v>-0.1089</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.06569999999999999</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4329</v>
+        <v>-0.173</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5661</v>
+        <v>0.1887</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5661</v>
+        <v>0.1887</v>
       </c>
       <c r="S14" t="n">
-        <v>1.335</v>
+        <v>0.665</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9123</v>
+        <v>0.6138</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4227</v>
+        <v>0.0512</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. BERENGUER DEL VALLE</t>
+          <t>I. NAVARRO SARMIENTO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3759</v>
+        <v>1.3126</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9978</v>
+        <v>0.8753</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3781</v>
+        <v>0.4373</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5674</v>
+        <v>-0.4382</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1064</v>
+        <v>0.0188</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4609</v>
+        <v>-0.457</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6762</v>
+        <v>0.0604</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0423</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.634</v>
+        <v>-0.0241</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1089</v>
+        <v>-0.4986</v>
       </c>
       <c r="N15" t="n">
-        <v>0.06419999999999999</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.173</v>
+        <v>-0.4329</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1887</v>
+        <v>0.5661</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1887</v>
+        <v>0.5661</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0218</v>
+        <v>1.1846</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3215</v>
+        <v>0.8148</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3433</v>
+        <v>0.3698</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3741</v>
+        <v>1.0084</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0006</v>
+        <v>1.6109</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6264999999999999</v>
+        <v>-0.6025</v>
       </c>
       <c r="G16" t="n">
         <v>0.4575</v>
@@ -1702,13 +1702,13 @@
         <v>1.1322</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8976</v>
+        <v>0.532</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.4173</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0906</v>
+        <v>0.1147</v>
       </c>
       <c r="V16" t="n">
         <v>0.019</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0722</v>
+        <v>0.1167</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0047</v>
+        <v>0.1021</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0675</v>
+        <v>0.0146</v>
       </c>
       <c r="G18" t="n">
         <v>1.9435</v>
@@ -1858,13 +1858,13 @@
         <v>0.5661</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2486</v>
+        <v>-0.2041</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1176</v>
+        <v>-0.0201</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1311</v>
+        <v>-0.184</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3018</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2167</v>
+        <v>-0.916</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5968</v>
+        <v>-0.4019</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6199</v>
+        <v>-0.514</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9809</v>
@@ -1936,13 +1936,13 @@
         <v>0.5661</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8018</v>
+        <v>-0.5011</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0929</v>
+        <v>0.102</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7089</v>
+        <v>-0.6031</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. LOPEZ RICO</t>
+          <t>J. CALERO SEVILLANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9805</v>
+        <v>-1.7234</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3342</v>
+        <v>-1.2929</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6463</v>
+        <v>-0.4305</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5687</v>
+        <v>0.5712</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6489</v>
+        <v>-2.4182</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0803</v>
+        <v>2.9894</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7196</v>
+        <v>0.8929</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.843</v>
+        <v>-1.2303</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1234</v>
+        <v>2.1232</v>
       </c>
       <c r="M20" t="n">
-        <v>0.151</v>
+        <v>-0.3217</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1941</v>
+        <v>-1.188</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0431</v>
+        <v>0.8663</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7548</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7548</v>
+        <v>1.6983</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3238</v>
+        <v>-0.6721</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3855</v>
+        <v>-0.1101</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0617</v>
+        <v>-0.5619</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4904</v>
+        <v>-1.2452</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4904</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7235</v>
+        <v>-2.0163</v>
       </c>
       <c r="E21" t="n">
         <v>-2.312</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4116</v>
+        <v>0.2956</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4793</v>
@@ -2092,13 +2092,13 @@
         <v>1.5096</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3197</v>
+        <v>-0.6125</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0312</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2885</v>
+        <v>-0.5813</v>
       </c>
       <c r="V21" t="n">
         <v>0.6415999999999999</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CALERO SEVILLANO</t>
+          <t>M. LOPEZ RICO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8049</v>
+        <v>-2.7924</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1698</v>
+        <v>-1.4059</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6351</v>
+        <v>-1.3865</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5712</v>
+        <v>-1.5687</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.4182</v>
+        <v>-1.6489</v>
       </c>
       <c r="I22" t="n">
-        <v>2.9894</v>
+        <v>0.0803</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8929</v>
+        <v>-1.7196</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2303</v>
+        <v>-1.843</v>
       </c>
       <c r="L22" t="n">
-        <v>2.1232</v>
+        <v>0.1234</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3217</v>
+        <v>0.151</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.188</v>
+        <v>0.1941</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8663</v>
+        <v>-0.0431</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3774</v>
+        <v>0.7548</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6983</v>
+        <v>0.7548</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7535</v>
+        <v>0.5118</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9871</v>
+        <v>0.3137</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7665</v>
+        <v>0.1981</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2452</v>
+        <v>-2.4904</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2452</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4276</v>
+        <v>-3.4821</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1899</v>
+        <v>-1.2155</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2378</v>
+        <v>-2.2666</v>
       </c>
       <c r="G23" t="n">
         <v>-4.0962</v>
@@ -2248,13 +2248,13 @@
         <v>1.887</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8976</v>
+        <v>0.0479</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5973000000000001</v>
+        <v>0.377</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3003</v>
+        <v>-0.3291</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9434</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7978</v>
+        <v>-4.8355</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8588</v>
+        <v>-1.0794</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.939</v>
+        <v>-3.7562</v>
       </c>
       <c r="G24" t="n">
         <v>-4.2452</v>
@@ -2326,13 +2326,13 @@
         <v>1.1322</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7413</v>
+        <v>0.221</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6438</v>
+        <v>0.1357</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0975</v>
+        <v>0.0853</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6226</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.1089</v>
+        <v>-7.8861</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.5076</v>
+        <v>-5.6768</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.6014</v>
+        <v>-2.2093</v>
       </c>
       <c r="G25" t="n">
         <v>-1.7636</v>
@@ -2404,13 +2404,13 @@
         <v>1.887</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7871</v>
+        <v>0.01</v>
       </c>
       <c r="T25" t="n">
-        <v>2.0597</v>
+        <v>0.8905</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.2726</v>
+        <v>-0.8804999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2262</v>
@@ -2437,22 +2437,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.1561</v>
+        <v>-16.2074</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.2751</v>
+        <v>-5.274999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-12.8813</v>
+        <v>-10.9326</v>
       </c>
       <c r="G26" t="n">
         <v>-9.376399999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-9.9155</v>
+        <v>-9.915499999999998</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5390000000000001</v>
+        <v>0.5389999999999993</v>
       </c>
       <c r="J26" t="n">
         <v>2.5223</v>
@@ -2461,7 +2461,7 @@
         <v>-1.3695</v>
       </c>
       <c r="L26" t="n">
-        <v>3.8921</v>
+        <v>3.892100000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-11.8986</v>
@@ -2482,16 +2482,16 @@
         <v>13.209</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4026999999999999</v>
+        <v>1.5459</v>
       </c>
       <c r="T26" t="n">
-        <v>3.940699999999999</v>
+        <v>3.9408</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.343599999999999</v>
+        <v>-2.3948</v>
       </c>
       <c r="V26" t="n">
-        <v>-4.603</v>
+        <v>-4.603000000000002</v>
       </c>
       <c r="W26" t="n">
         <v>5.2446</v>
